--- a/test/samples/system/expected/BcmTest/BcmGreenTables.xlsx
+++ b/test/samples/system/expected/BcmTest/BcmGreenTables.xlsx
@@ -7,16 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_INPUT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_OUTPUT" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_INPUT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_OUTPUT" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_RECEIVE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_SEND" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_RECEIVE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_SEND" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LIT_INPUT'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LIT_OUTPUT'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TUR_INPUT'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TUR_OUTPUT'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LIT_RECEIVE'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LIT_SEND'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TUR_RECEIVE'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TUR_SEND'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -627,8 +627,6 @@
           <t>Power mode test</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>PowerMode</t>
@@ -787,8 +785,6 @@
           <t>Position lamp test</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>PositionActive</t>
@@ -956,8 +952,6 @@
           <t>Position lamp test</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>PositionActive</t>
@@ -1119,8 +1113,6 @@
           <t>Power mode test</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>PowerMode</t>

--- a/test/samples/system/expected/BcmTest/BcmGreenTables.xlsx
+++ b/test/samples/system/expected/BcmTest/BcmGreenTables.xlsx
@@ -7,16 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_RECEIVE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_SEND" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_RECEIVE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_SEND" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_R-Port" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_P-Port" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_R-Port" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_P-Port" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LIT_RECEIVE'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LIT_SEND'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TUR_RECEIVE'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TUR_SEND'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LIT_R-Port'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LIT_P-Port'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TUR_R-Port'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TUR_P-Port'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/test/samples/system/expected/BcmTest/BcmGreenTables.xlsx
+++ b/test/samples/system/expected/BcmTest/BcmGreenTables.xlsx
@@ -7,16 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_INPUT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_OUTPUT" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_INPUT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_OUTPUT" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_R-Port" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIT_P-Port" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_R-Port" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUR_P-Port" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LIT_INPUT'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LIT_OUTPUT'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TUR_INPUT'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TUR_OUTPUT'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LIT_R-Port'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LIT_P-Port'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TUR_R-Port'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TUR_P-Port'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -627,8 +627,6 @@
           <t>Power mode test</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>PowerMode</t>
@@ -787,8 +785,6 @@
           <t>Position lamp test</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>PositionActive</t>
@@ -956,8 +952,6 @@
           <t>Position lamp test</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>PositionActive</t>
@@ -1119,8 +1113,6 @@
           <t>Power mode test</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>PowerMode</t>
